--- a/artfynd/A 22297-2024 artfynd.xlsx
+++ b/artfynd/A 22297-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106185518</v>
+        <v>106185311</v>
       </c>
       <c r="B2" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1639</v>
+        <v>1460</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588243.5404531289</v>
+        <v>588271</v>
       </c>
       <c r="R2" t="n">
-        <v>6379252.662372959</v>
+        <v>6379405</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106185463</v>
+        <v>106185518</v>
       </c>
       <c r="B3" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>1639</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588243.0145082733</v>
+        <v>588244</v>
       </c>
       <c r="R3" t="n">
-        <v>6379252.114139655</v>
+        <v>6379253</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +845,9 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +876,404 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106185321</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sundslyckan, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>588270</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6379400</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-01-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>klippa</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106185392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sundslyckan, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>588270</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6379400</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-01-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106185463</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sundslyckan, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>588243</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6379252</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-01-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123165741</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>E22 Målbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>588463</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6379312</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22297-2024 artfynd.xlsx
+++ b/artfynd/A 22297-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185311</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185321</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185463</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,8 +1304,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123165741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>